--- a/docs/downloads/经营分_鲁西省区__济南中片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__济南中片区_2026-10-18.xlsx
@@ -1035,33 +1035,33 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7037686496480757774</t>
+          <t>7235875058416912445</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（3.0版济南高新万达广场天辰路店）</t>
+          <t>7天优品Premium（济南齐鲁软件园店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(济南高新万达广场天辰路店)</t>
+          <t>7天优品Premium(济南历下区舜华路齐鲁软件园)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1071,13 +1071,13 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
         <v>30</v>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7235875058416912445</t>
+          <t>7325695095246686217</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7天优品Premium（济南齐鲁软件园店）</t>
+          <t>维也纳酒店（5.0济南奥体CBD万象城店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7天优品Premium(济南历下区舜华路齐鲁软件园)</t>
+          <t>维也纳酒店(济南CBD中央商务区店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7325695095246686217</t>
+          <t>7398800005836605503</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南奥体CBD万象城店）</t>
+          <t>维纳斯皇家酒店（济南大明湖店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南CBD中央商务区店)</t>
+          <t>维纳斯皇家酒店(大明湖地铁站店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7398800005836605503</t>
+          <t>7116631532303091749</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维纳斯皇家酒店（济南大明湖店）</t>
+          <t>希岸·轻雅酒店（济南花园东路地铁站环联夜市店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维纳斯皇家酒店(大明湖地铁站店)</t>
+          <t>希岸·轻雅酒店(济南花园东路地铁站环联夜市店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1335,19 +1335,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1387,33 +1387,33 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7116631532303091749</t>
+          <t>7037686496480757774</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店（济南花园东路地铁站环联夜市店）</t>
+          <t>凯里亚德酒店（3.0版济南高新万达广场天辰路店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(济南花园东路地铁站环联夜市店)</t>
+          <t>凯里亚德酒店(济南高新万达广场天辰路店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1423,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2925,13 +2925,13 @@
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3250,14 +3250,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
